--- a/output/yearly_population_iteration_2_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_2_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5291</v>
+        <v>5794</v>
       </c>
       <c r="C2" t="n">
-        <v>12314</v>
+        <v>6942</v>
       </c>
       <c r="D2" t="n">
-        <v>22682</v>
+        <v>22093</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3796</v>
+        <v>3956</v>
       </c>
       <c r="C3" t="n">
-        <v>4363</v>
+        <v>5269</v>
       </c>
       <c r="D3" t="n">
-        <v>17851</v>
+        <v>16510</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2941</v>
+        <v>3329</v>
       </c>
       <c r="C4" t="n">
-        <v>5294</v>
+        <v>4404</v>
       </c>
       <c r="D4" t="n">
-        <v>9435</v>
+        <v>8669</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1834</v>
+        <v>1958</v>
       </c>
       <c r="C5" t="n">
-        <v>4574</v>
+        <v>3801</v>
       </c>
       <c r="D5" t="n">
-        <v>3467</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>987</v>
+        <v>964</v>
       </c>
       <c r="C6" t="n">
-        <v>3369</v>
+        <v>2766</v>
       </c>
       <c r="D6" t="n">
-        <v>1327</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>476</v>
+        <v>415</v>
       </c>
       <c r="C7" t="n">
-        <v>1949</v>
+        <v>1885</v>
       </c>
       <c r="D7" t="n">
-        <v>679</v>
+        <v>676</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>178</v>
+        <v>153</v>
       </c>
       <c r="C8" t="n">
-        <v>880</v>
+        <v>976</v>
       </c>
       <c r="D8" t="n">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C9" t="n">
-        <v>365</v>
+        <v>421</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10">
@@ -892,10 +892,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="D10" t="n">
         <v>244</v>
@@ -912,7 +912,7 @@
         <v>163</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -923,7 +923,7 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D12" t="n">
         <v>162</v>
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -965,7 +965,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
         <v>81</v>
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1007,7 +1007,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1049,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D21" t="n">
         <v>8</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6962</v>
+        <v>6975</v>
       </c>
       <c r="C2" t="n">
-        <v>13260</v>
+        <v>8366</v>
       </c>
       <c r="D2" t="n">
-        <v>20275</v>
+        <v>23718</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3633</v>
+        <v>3889</v>
       </c>
       <c r="C3" t="n">
-        <v>6906</v>
+        <v>5300</v>
       </c>
       <c r="D3" t="n">
-        <v>17298</v>
+        <v>16159</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2822</v>
+        <v>3083</v>
       </c>
       <c r="C4" t="n">
-        <v>4704</v>
+        <v>4677</v>
       </c>
       <c r="D4" t="n">
-        <v>10350</v>
+        <v>9685</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2027</v>
+        <v>2238</v>
       </c>
       <c r="C5" t="n">
-        <v>4803</v>
+        <v>3999</v>
       </c>
       <c r="D5" t="n">
-        <v>4278</v>
+        <v>3992</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1227</v>
+        <v>1266</v>
       </c>
       <c r="C6" t="n">
-        <v>3824</v>
+        <v>3169</v>
       </c>
       <c r="D6" t="n">
-        <v>1604</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>614</v>
+        <v>574</v>
       </c>
       <c r="C7" t="n">
-        <v>2541</v>
+        <v>2254</v>
       </c>
       <c r="D7" t="n">
-        <v>767</v>
+        <v>751</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>262</v>
+        <v>229</v>
       </c>
       <c r="C8" t="n">
-        <v>1330</v>
+        <v>1367</v>
       </c>
       <c r="D8" t="n">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="C9" t="n">
-        <v>568</v>
+        <v>645</v>
       </c>
       <c r="D9" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C10" t="n">
-        <v>271</v>
+        <v>301</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -1251,7 +1251,7 @@
         <v>106</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1318,7 +1318,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1360,7 +1360,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8542</v>
+        <v>8534</v>
       </c>
       <c r="C2" t="n">
-        <v>16245</v>
+        <v>9828</v>
       </c>
       <c r="D2" t="n">
-        <v>18156</v>
+        <v>19954</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4010</v>
+        <v>4174</v>
       </c>
       <c r="C3" t="n">
-        <v>8380</v>
+        <v>5810</v>
       </c>
       <c r="D3" t="n">
-        <v>16548</v>
+        <v>16031</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2708</v>
+        <v>2940</v>
       </c>
       <c r="C4" t="n">
-        <v>5491</v>
+        <v>4803</v>
       </c>
       <c r="D4" t="n">
-        <v>10936</v>
+        <v>10229</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2077</v>
+        <v>2289</v>
       </c>
       <c r="C5" t="n">
-        <v>4662</v>
+        <v>4163</v>
       </c>
       <c r="D5" t="n">
-        <v>5022</v>
+        <v>4690</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1396</v>
+        <v>1495</v>
       </c>
       <c r="C6" t="n">
-        <v>4138</v>
+        <v>3483</v>
       </c>
       <c r="D6" t="n">
-        <v>1926</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>759</v>
+        <v>753</v>
       </c>
       <c r="C7" t="n">
-        <v>3018</v>
+        <v>2598</v>
       </c>
       <c r="D7" t="n">
-        <v>874</v>
+        <v>848</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>348</v>
+        <v>318</v>
       </c>
       <c r="C8" t="n">
-        <v>1792</v>
+        <v>1714</v>
       </c>
       <c r="D8" t="n">
-        <v>488</v>
+        <v>497</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="C9" t="n">
-        <v>838</v>
+        <v>907</v>
       </c>
       <c r="D9" t="n">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C10" t="n">
-        <v>373</v>
+        <v>422</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>255</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -1604,7 +1604,7 @@
         <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1629,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7764</v>
+        <v>7725</v>
       </c>
       <c r="C2" t="n">
-        <v>11306</v>
+        <v>6683</v>
       </c>
       <c r="D2" t="n">
-        <v>15319</v>
+        <v>16578</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4801</v>
+        <v>5172</v>
       </c>
       <c r="C3" t="n">
-        <v>12053</v>
+        <v>8693</v>
       </c>
       <c r="D3" t="n">
-        <v>18451</v>
+        <v>17916</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1919</v>
+        <v>2115</v>
       </c>
       <c r="C4" t="n">
-        <v>7427</v>
+        <v>6670</v>
       </c>
       <c r="D4" t="n">
-        <v>10610</v>
+        <v>9919</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1289</v>
+        <v>1381</v>
       </c>
       <c r="C5" t="n">
-        <v>4055</v>
+        <v>3413</v>
       </c>
       <c r="D5" t="n">
-        <v>3237</v>
+        <v>3085</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="C6" t="n">
-        <v>2957</v>
+        <v>2546</v>
       </c>
       <c r="D6" t="n">
-        <v>856</v>
+        <v>831</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>321</v>
+        <v>293</v>
       </c>
       <c r="C7" t="n">
-        <v>1756</v>
+        <v>1679</v>
       </c>
       <c r="D7" t="n">
-        <v>478</v>
+        <v>487</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="C8" t="n">
-        <v>821</v>
+        <v>888</v>
       </c>
       <c r="D8" t="n">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>365</v>
+        <v>413</v>
       </c>
       <c r="D9" t="n">
-        <v>244</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15">
@@ -1901,7 +1901,7 @@
         <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
         <v>38</v>
@@ -1968,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D20" t="n">
         <v>10</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4599</v>
+        <v>4633</v>
       </c>
       <c r="C2" t="n">
-        <v>5498</v>
+        <v>3129</v>
       </c>
       <c r="D2" t="n">
-        <v>10710</v>
+        <v>11675</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5162</v>
+        <v>5380</v>
       </c>
       <c r="C3" t="n">
-        <v>10654</v>
+        <v>7119</v>
       </c>
       <c r="D3" t="n">
-        <v>17139</v>
+        <v>16702</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2592</v>
+        <v>2849</v>
       </c>
       <c r="C4" t="n">
-        <v>9573</v>
+        <v>7655</v>
       </c>
       <c r="D4" t="n">
-        <v>11518</v>
+        <v>11036</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1440</v>
+        <v>1560</v>
       </c>
       <c r="C5" t="n">
-        <v>5524</v>
+        <v>4850</v>
       </c>
       <c r="D5" t="n">
-        <v>4151</v>
+        <v>3903</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>826</v>
+        <v>837</v>
       </c>
       <c r="C6" t="n">
-        <v>3506</v>
+        <v>2975</v>
       </c>
       <c r="D6" t="n">
-        <v>1076</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>300</v>
+        <v>276</v>
       </c>
       <c r="C7" t="n">
-        <v>2198</v>
+        <v>2064</v>
       </c>
       <c r="D7" t="n">
-        <v>523</v>
+        <v>533</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="C8" t="n">
-        <v>1092</v>
+        <v>1152</v>
       </c>
       <c r="D8" t="n">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C9" t="n">
-        <v>403</v>
+        <v>462</v>
       </c>
       <c r="D9" t="n">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11">
@@ -2150,10 +2150,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
         <v>167</v>
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
         <v>37</v>
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D19" t="n">
         <v>9</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4686</v>
+        <v>5085</v>
       </c>
       <c r="C2" t="n">
-        <v>12476</v>
+        <v>3911</v>
       </c>
       <c r="D2" t="n">
-        <v>14336</v>
+        <v>17162</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4184</v>
+        <v>4252</v>
       </c>
       <c r="C3" t="n">
-        <v>7313</v>
+        <v>4650</v>
       </c>
       <c r="D3" t="n">
-        <v>15112</v>
+        <v>14989</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3128</v>
+        <v>3405</v>
       </c>
       <c r="C4" t="n">
-        <v>9892</v>
+        <v>7233</v>
       </c>
       <c r="D4" t="n">
-        <v>12085</v>
+        <v>11625</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1704</v>
+        <v>1869</v>
       </c>
       <c r="C5" t="n">
-        <v>7327</v>
+        <v>6068</v>
       </c>
       <c r="D5" t="n">
-        <v>5156</v>
+        <v>4879</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>984</v>
+        <v>1037</v>
       </c>
       <c r="C6" t="n">
-        <v>4344</v>
+        <v>3821</v>
       </c>
       <c r="D6" t="n">
-        <v>1504</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="C7" t="n">
-        <v>2769</v>
+        <v>2455</v>
       </c>
       <c r="D7" t="n">
-        <v>593</v>
+        <v>600</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="C8" t="n">
-        <v>1535</v>
+        <v>1538</v>
       </c>
       <c r="D8" t="n">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="9">
@@ -2433,10 +2433,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>656</v>
+        <v>734</v>
       </c>
       <c r="D9" t="n">
         <v>263</v>
@@ -2450,10 +2450,10 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>286</v>
+        <v>316</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11">
@@ -2461,10 +2461,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
         <v>170</v>
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14">
@@ -2509,7 +2509,7 @@
         <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2523,7 +2523,7 @@
         <v>43</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D19" t="n">
         <v>6</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2808</v>
+        <v>3013</v>
       </c>
       <c r="C2" t="n">
-        <v>5929</v>
+        <v>1819</v>
       </c>
       <c r="D2" t="n">
-        <v>10044</v>
+        <v>11864</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4186</v>
+        <v>4295</v>
       </c>
       <c r="C3" t="n">
-        <v>8795</v>
+        <v>4246</v>
       </c>
       <c r="D3" t="n">
-        <v>14692</v>
+        <v>14872</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3423</v>
+        <v>3753</v>
       </c>
       <c r="C4" t="n">
-        <v>9913</v>
+        <v>6978</v>
       </c>
       <c r="D4" t="n">
-        <v>12608</v>
+        <v>12310</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1762</v>
+        <v>1918</v>
       </c>
       <c r="C5" t="n">
-        <v>8949</v>
+        <v>7190</v>
       </c>
       <c r="D5" t="n">
-        <v>5410</v>
+        <v>5128</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>800</v>
+        <v>824</v>
       </c>
       <c r="C6" t="n">
-        <v>5163</v>
+        <v>4676</v>
       </c>
       <c r="D6" t="n">
-        <v>1457</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="C7" t="n">
-        <v>2843</v>
+        <v>2660</v>
       </c>
       <c r="D7" t="n">
-        <v>587</v>
+        <v>594</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C8" t="n">
-        <v>1094</v>
+        <v>1201</v>
       </c>
       <c r="D8" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>280</v>
+        <v>309</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10">
@@ -2758,10 +2758,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="D10" t="n">
         <v>166</v>
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -2806,7 +2806,7 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -2820,7 +2820,7 @@
         <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D18" t="n">
         <v>5</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2888</v>
+        <v>3268</v>
       </c>
       <c r="C2" t="n">
-        <v>7358</v>
+        <v>3979</v>
       </c>
       <c r="D2" t="n">
-        <v>12500</v>
+        <v>10125</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3109</v>
+        <v>3207</v>
       </c>
       <c r="C3" t="n">
-        <v>6667</v>
+        <v>2780</v>
       </c>
       <c r="D3" t="n">
-        <v>13133</v>
+        <v>13463</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3280</v>
+        <v>3510</v>
       </c>
       <c r="C4" t="n">
-        <v>9286</v>
+        <v>5588</v>
       </c>
       <c r="D4" t="n">
-        <v>12544</v>
+        <v>12353</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2131</v>
+        <v>2356</v>
       </c>
       <c r="C5" t="n">
-        <v>9265</v>
+        <v>7013</v>
       </c>
       <c r="D5" t="n">
-        <v>6282</v>
+        <v>6124</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1035</v>
+        <v>1122</v>
       </c>
       <c r="C6" t="n">
-        <v>6694</v>
+        <v>5740</v>
       </c>
       <c r="D6" t="n">
-        <v>1983</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C7" t="n">
-        <v>3784</v>
+        <v>3521</v>
       </c>
       <c r="D7" t="n">
-        <v>683</v>
+        <v>698</v>
       </c>
     </row>
     <row r="8">
@@ -3041,10 +3041,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C8" t="n">
-        <v>1714</v>
+        <v>1753</v>
       </c>
       <c r="D8" t="n">
         <v>395</v>
@@ -3058,10 +3058,10 @@
         <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>535</v>
+        <v>606</v>
       </c>
       <c r="D9" t="n">
-        <v>290</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D12" t="n">
         <v>99</v>
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D17" t="n">
         <v>9</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2177</v>
+        <v>2446</v>
       </c>
       <c r="C2" t="n">
-        <v>4476</v>
+        <v>2373</v>
       </c>
       <c r="D2" t="n">
-        <v>9791</v>
+        <v>7968</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2669</v>
+        <v>2826</v>
       </c>
       <c r="C3" t="n">
-        <v>6371</v>
+        <v>2985</v>
       </c>
       <c r="D3" t="n">
-        <v>12368</v>
+        <v>12330</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2949</v>
+        <v>3149</v>
       </c>
       <c r="C4" t="n">
-        <v>8265</v>
+        <v>4473</v>
       </c>
       <c r="D4" t="n">
-        <v>12356</v>
+        <v>12245</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2339</v>
+        <v>2581</v>
       </c>
       <c r="C5" t="n">
-        <v>9435</v>
+        <v>6549</v>
       </c>
       <c r="D5" t="n">
-        <v>6872</v>
+        <v>6772</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1197</v>
+        <v>1328</v>
       </c>
       <c r="C6" t="n">
-        <v>7719</v>
+        <v>6384</v>
       </c>
       <c r="D6" t="n">
-        <v>2328</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>264</v>
+        <v>281</v>
       </c>
       <c r="C7" t="n">
-        <v>4697</v>
+        <v>4326</v>
       </c>
       <c r="D7" t="n">
-        <v>771</v>
+        <v>796</v>
       </c>
     </row>
     <row r="8">
@@ -3355,10 +3355,10 @@
         <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>2179</v>
+        <v>2242</v>
       </c>
       <c r="D8" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>590</v>
+        <v>701</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="D10" t="n">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D13" t="n">
         <v>62</v>
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3950</v>
+        <v>3466</v>
       </c>
       <c r="C2" t="n">
-        <v>14738</v>
+        <v>6758</v>
       </c>
       <c r="D2" t="n">
-        <v>13826</v>
+        <v>15500</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2110</v>
+        <v>2260</v>
       </c>
       <c r="C3" t="n">
-        <v>5051</v>
+        <v>2449</v>
       </c>
       <c r="D3" t="n">
-        <v>11307</v>
+        <v>11017</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2481</v>
+        <v>2661</v>
       </c>
       <c r="C4" t="n">
-        <v>7329</v>
+        <v>3737</v>
       </c>
       <c r="D4" t="n">
-        <v>11981</v>
+        <v>11884</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2338</v>
+        <v>2533</v>
       </c>
       <c r="C5" t="n">
-        <v>8789</v>
+        <v>5555</v>
       </c>
       <c r="D5" t="n">
-        <v>7281</v>
+        <v>7236</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1434</v>
+        <v>1634</v>
       </c>
       <c r="C6" t="n">
-        <v>8283</v>
+        <v>6394</v>
       </c>
       <c r="D6" t="n">
-        <v>2865</v>
+        <v>2849</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>484</v>
+        <v>547</v>
       </c>
       <c r="C7" t="n">
-        <v>5761</v>
+        <v>5110</v>
       </c>
       <c r="D7" t="n">
-        <v>946</v>
+        <v>976</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="C8" t="n">
-        <v>3038</v>
+        <v>3018</v>
       </c>
       <c r="D8" t="n">
-        <v>444</v>
+        <v>452</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>1072</v>
+        <v>1221</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10">
@@ -3691,10 +3691,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>324</v>
+        <v>375</v>
       </c>
       <c r="D10" t="n">
         <v>189</v>
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -3753,7 +3753,7 @@
         <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6294</v>
+        <v>4550</v>
       </c>
       <c r="C2" t="n">
-        <v>7258</v>
+        <v>9719</v>
       </c>
       <c r="D2" t="n">
-        <v>16335</v>
+        <v>11403</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2885</v>
+        <v>2455</v>
       </c>
       <c r="C2" t="n">
-        <v>8724</v>
+        <v>3785</v>
       </c>
       <c r="D2" t="n">
-        <v>10287</v>
+        <v>11408</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2927</v>
+        <v>3097</v>
       </c>
       <c r="C3" t="n">
-        <v>7596</v>
+        <v>3690</v>
       </c>
       <c r="D3" t="n">
-        <v>12549</v>
+        <v>12366</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3406</v>
+        <v>3675</v>
       </c>
       <c r="C4" t="n">
-        <v>10306</v>
+        <v>5522</v>
       </c>
       <c r="D4" t="n">
-        <v>12329</v>
+        <v>12277</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1346</v>
+        <v>1603</v>
       </c>
       <c r="C5" t="n">
-        <v>12140</v>
+        <v>8629</v>
       </c>
       <c r="D5" t="n">
-        <v>6674</v>
+        <v>6675</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>447</v>
+        <v>505</v>
       </c>
       <c r="C6" t="n">
-        <v>7106</v>
+        <v>6323</v>
       </c>
       <c r="D6" t="n">
-        <v>2191</v>
+        <v>2228</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="C7" t="n">
-        <v>2977</v>
+        <v>2957</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>567</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>1050</v>
+        <v>1196</v>
       </c>
       <c r="D8" t="n">
-        <v>289</v>
+        <v>298</v>
       </c>
     </row>
     <row r="9">
@@ -4299,10 +4299,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>317</v>
+        <v>367</v>
       </c>
       <c r="D9" t="n">
         <v>185</v>
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="D10" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12">
@@ -4361,7 +4361,7 @@
         <v>37</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6605</v>
+        <v>5725</v>
       </c>
       <c r="C2" t="n">
-        <v>6824</v>
+        <v>6370</v>
       </c>
       <c r="D2" t="n">
-        <v>20697</v>
+        <v>22597</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2674</v>
+        <v>1934</v>
       </c>
       <c r="C3" t="n">
-        <v>3658</v>
+        <v>4898</v>
       </c>
       <c r="D3" t="n">
-        <v>3383</v>
+        <v>2555</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4571,7 +4571,7 @@
         <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="D6" t="n">
         <v>816</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4736</v>
+        <v>4435</v>
       </c>
       <c r="C2" t="n">
-        <v>8814</v>
+        <v>3714</v>
       </c>
       <c r="D2" t="n">
-        <v>29522</v>
+        <v>30876</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3811</v>
+        <v>3143</v>
       </c>
       <c r="C3" t="n">
-        <v>4699</v>
+        <v>4942</v>
       </c>
       <c r="D3" t="n">
-        <v>6042</v>
+        <v>5734</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1196</v>
+        <v>874</v>
       </c>
       <c r="C4" t="n">
-        <v>2188</v>
+        <v>2914</v>
       </c>
       <c r="D4" t="n">
-        <v>1863</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D5" t="n">
         <v>1198</v>
@@ -4896,7 +4896,7 @@
         <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
         <v>584</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4938</v>
+        <v>5801</v>
       </c>
       <c r="C2" t="n">
-        <v>5582</v>
+        <v>6220</v>
       </c>
       <c r="D2" t="n">
-        <v>34370</v>
+        <v>27301</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3512</v>
+        <v>3104</v>
       </c>
       <c r="C3" t="n">
-        <v>5984</v>
+        <v>3715</v>
       </c>
       <c r="D3" t="n">
-        <v>9363</v>
+        <v>9343</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2131</v>
+        <v>1706</v>
       </c>
       <c r="C4" t="n">
-        <v>3519</v>
+        <v>3954</v>
       </c>
       <c r="D4" t="n">
-        <v>2608</v>
+        <v>2419</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>541</v>
+        <v>412</v>
       </c>
       <c r="C5" t="n">
-        <v>1294</v>
+        <v>1690</v>
       </c>
       <c r="D5" t="n">
-        <v>1271</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="6">
@@ -5193,7 +5193,7 @@
         <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D6" t="n">
         <v>908</v>
@@ -5207,7 +5207,7 @@
         <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D7" t="n">
         <v>626</v>
@@ -5221,7 +5221,7 @@
         <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D8" t="n">
         <v>454</v>
@@ -5232,7 +5232,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
         <v>268</v>
@@ -5260,7 +5260,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" t="n">
         <v>176</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5412</v>
+        <v>6933</v>
       </c>
       <c r="C2" t="n">
-        <v>9546</v>
+        <v>5844</v>
       </c>
       <c r="D2" t="n">
-        <v>33159</v>
+        <v>25686</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3432</v>
+        <v>3562</v>
       </c>
       <c r="C3" t="n">
-        <v>5041</v>
+        <v>4355</v>
       </c>
       <c r="D3" t="n">
-        <v>12504</v>
+        <v>11414</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2375</v>
+        <v>2015</v>
       </c>
       <c r="C4" t="n">
-        <v>4713</v>
+        <v>3743</v>
       </c>
       <c r="D4" t="n">
-        <v>3760</v>
+        <v>3608</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1101</v>
+        <v>871</v>
       </c>
       <c r="C5" t="n">
-        <v>2420</v>
+        <v>2828</v>
       </c>
       <c r="D5" t="n">
-        <v>1451</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>294</v>
+        <v>243</v>
       </c>
       <c r="C6" t="n">
-        <v>795</v>
+        <v>989</v>
       </c>
       <c r="D6" t="n">
-        <v>958</v>
+        <v>952</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="D7" t="n">
-        <v>666</v>
+        <v>660</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D8" t="n">
-        <v>471</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9">
@@ -5543,10 +5543,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D9" t="n">
         <v>380</v>
@@ -5560,7 +5560,7 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
         <v>342</v>
@@ -5571,7 +5571,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C11" t="n">
         <v>190</v>
@@ -5585,10 +5585,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D12" t="n">
         <v>217</v>
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5619,7 +5619,7 @@
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5644,7 +5644,7 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D16" t="n">
         <v>101</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7762</v>
+        <v>8317</v>
       </c>
       <c r="C2" t="n">
-        <v>6850</v>
+        <v>7325</v>
       </c>
       <c r="D2" t="n">
-        <v>37380</v>
+        <v>37899</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3174</v>
+        <v>3767</v>
       </c>
       <c r="C3" t="n">
-        <v>5983</v>
+        <v>4181</v>
       </c>
       <c r="D3" t="n">
-        <v>13889</v>
+        <v>12023</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1780</v>
+        <v>1728</v>
       </c>
       <c r="C4" t="n">
-        <v>4000</v>
+        <v>3305</v>
       </c>
       <c r="D4" t="n">
-        <v>4574</v>
+        <v>4295</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>900</v>
+        <v>744</v>
       </c>
       <c r="C5" t="n">
-        <v>2602</v>
+        <v>2407</v>
       </c>
       <c r="D5" t="n">
-        <v>1451</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>328</v>
+        <v>261</v>
       </c>
       <c r="C6" t="n">
-        <v>1076</v>
+        <v>1271</v>
       </c>
       <c r="D6" t="n">
-        <v>793</v>
+        <v>782</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C7" t="n">
-        <v>358</v>
+        <v>424</v>
       </c>
       <c r="D7" t="n">
-        <v>523</v>
+        <v>514</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
         <v>222</v>
       </c>
       <c r="D8" t="n">
-        <v>352</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
@@ -5874,7 +5874,7 @@
         <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -5896,7 +5896,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
         <v>92</v>
@@ -5910,7 +5910,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
         <v>73</v>
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
         <v>96</v>
@@ -5941,10 +5941,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6025,7 +6025,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5609</v>
+        <v>6392</v>
       </c>
       <c r="C2" t="n">
-        <v>7213</v>
+        <v>5248</v>
       </c>
       <c r="D2" t="n">
-        <v>31322</v>
+        <v>28818</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4527</v>
+        <v>5000</v>
       </c>
       <c r="C3" t="n">
-        <v>5580</v>
+        <v>5176</v>
       </c>
       <c r="D3" t="n">
-        <v>16813</v>
+        <v>15485</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2164</v>
+        <v>2405</v>
       </c>
       <c r="C4" t="n">
-        <v>5097</v>
+        <v>3766</v>
       </c>
       <c r="D4" t="n">
-        <v>6312</v>
+        <v>5681</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1190</v>
+        <v>1086</v>
       </c>
       <c r="C5" t="n">
-        <v>3353</v>
+        <v>2882</v>
       </c>
       <c r="D5" t="n">
-        <v>1992</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>559</v>
+        <v>464</v>
       </c>
       <c r="C6" t="n">
-        <v>1912</v>
+        <v>1898</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>888</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>190</v>
+        <v>156</v>
       </c>
       <c r="C7" t="n">
-        <v>748</v>
+        <v>896</v>
       </c>
       <c r="D7" t="n">
-        <v>567</v>
+        <v>553</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>295</v>
+        <v>330</v>
       </c>
       <c r="D8" t="n">
-        <v>375</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -6165,10 +6165,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D9" t="n">
         <v>283</v>
@@ -6185,7 +6185,7 @@
         <v>172</v>
       </c>
       <c r="D10" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11">
@@ -6193,7 +6193,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" t="n">
         <v>131</v>
@@ -6221,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
         <v>119</v>
@@ -6235,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
         <v>63</v>
@@ -6255,7 +6255,7 @@
         <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6294,7 +6294,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6336,7 +6336,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5149</v>
+        <v>4846</v>
       </c>
       <c r="C2" t="n">
-        <v>4340</v>
+        <v>7575</v>
       </c>
       <c r="D2" t="n">
-        <v>26473</v>
+        <v>24437</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4159</v>
+        <v>4720</v>
       </c>
       <c r="C3" t="n">
-        <v>5592</v>
+        <v>4522</v>
       </c>
       <c r="D3" t="n">
-        <v>17834</v>
+        <v>16503</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2846</v>
+        <v>3130</v>
       </c>
       <c r="C4" t="n">
-        <v>5206</v>
+        <v>4472</v>
       </c>
       <c r="D4" t="n">
-        <v>7974</v>
+        <v>7390</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1452</v>
+        <v>1514</v>
       </c>
       <c r="C5" t="n">
-        <v>4220</v>
+        <v>3269</v>
       </c>
       <c r="D5" t="n">
-        <v>2719</v>
+        <v>2540</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>789</v>
+        <v>691</v>
       </c>
       <c r="C6" t="n">
-        <v>2637</v>
+        <v>2395</v>
       </c>
       <c r="D6" t="n">
-        <v>1073</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>323</v>
+        <v>272</v>
       </c>
       <c r="C7" t="n">
-        <v>1340</v>
+        <v>1416</v>
       </c>
       <c r="D7" t="n">
-        <v>621</v>
+        <v>606</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="C8" t="n">
-        <v>513</v>
+        <v>612</v>
       </c>
       <c r="D8" t="n">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6521,7 +6521,7 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
         <v>158</v>
@@ -6532,7 +6532,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
         <v>89</v>
@@ -6546,10 +6546,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
         <v>99</v>
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -6577,7 +6577,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
         <v>64</v>
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6647,7 +6647,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
         <v>7</v>

--- a/output/yearly_population_iteration_2_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_2_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5794</v>
+        <v>6811</v>
       </c>
       <c r="C2" t="n">
-        <v>6942</v>
+        <v>7212</v>
       </c>
       <c r="D2" t="n">
-        <v>22093</v>
+        <v>20755</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3956</v>
+        <v>4720</v>
       </c>
       <c r="C3" t="n">
-        <v>5269</v>
+        <v>6244</v>
       </c>
       <c r="D3" t="n">
-        <v>16510</v>
+        <v>11547</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3329</v>
+        <v>3388</v>
       </c>
       <c r="C4" t="n">
-        <v>4404</v>
+        <v>5138</v>
       </c>
       <c r="D4" t="n">
-        <v>8669</v>
+        <v>5301</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1958</v>
+        <v>2225</v>
       </c>
       <c r="C5" t="n">
-        <v>3801</v>
+        <v>3664</v>
       </c>
       <c r="D5" t="n">
-        <v>3300</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>964</v>
+        <v>1262</v>
       </c>
       <c r="C6" t="n">
-        <v>2766</v>
+        <v>2900</v>
       </c>
       <c r="D6" t="n">
-        <v>1281</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>415</v>
+        <v>579</v>
       </c>
       <c r="C7" t="n">
-        <v>1885</v>
+        <v>1727</v>
       </c>
       <c r="D7" t="n">
-        <v>676</v>
+        <v>643</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>153</v>
+        <v>214</v>
       </c>
       <c r="C8" t="n">
-        <v>976</v>
+        <v>732</v>
       </c>
       <c r="D8" t="n">
-        <v>432</v>
+        <v>442</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>421</v>
+        <v>299</v>
       </c>
       <c r="D9" t="n">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
@@ -1010,7 +1010,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1052,7 +1052,7 @@
         <v>99</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6975</v>
+        <v>9040</v>
       </c>
       <c r="C2" t="n">
-        <v>8366</v>
+        <v>14831</v>
       </c>
       <c r="D2" t="n">
-        <v>23718</v>
+        <v>31694</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3889</v>
+        <v>4635</v>
       </c>
       <c r="C3" t="n">
-        <v>5300</v>
+        <v>5879</v>
       </c>
       <c r="D3" t="n">
-        <v>16159</v>
+        <v>12023</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3083</v>
+        <v>3432</v>
       </c>
       <c r="C4" t="n">
-        <v>4677</v>
+        <v>5523</v>
       </c>
       <c r="D4" t="n">
-        <v>9685</v>
+        <v>6108</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2238</v>
+        <v>2417</v>
       </c>
       <c r="C5" t="n">
-        <v>3999</v>
+        <v>4295</v>
       </c>
       <c r="D5" t="n">
-        <v>3992</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1266</v>
+        <v>1533</v>
       </c>
       <c r="C6" t="n">
-        <v>3169</v>
+        <v>3194</v>
       </c>
       <c r="D6" t="n">
-        <v>1573</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>574</v>
+        <v>791</v>
       </c>
       <c r="C7" t="n">
-        <v>2254</v>
+        <v>2266</v>
       </c>
       <c r="D7" t="n">
-        <v>751</v>
+        <v>699</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>229</v>
+        <v>324</v>
       </c>
       <c r="C8" t="n">
-        <v>1367</v>
+        <v>1170</v>
       </c>
       <c r="D8" t="n">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="C9" t="n">
-        <v>645</v>
+        <v>478</v>
       </c>
       <c r="D9" t="n">
-        <v>317</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C10" t="n">
-        <v>301</v>
+        <v>243</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1262,7 +1262,7 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
         <v>101</v>
@@ -1279,7 +1279,7 @@
         <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1321,7 +1321,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8534</v>
+        <v>9268</v>
       </c>
       <c r="C2" t="n">
-        <v>9828</v>
+        <v>10590</v>
       </c>
       <c r="D2" t="n">
-        <v>19954</v>
+        <v>31613</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4174</v>
+        <v>5229</v>
       </c>
       <c r="C3" t="n">
-        <v>5810</v>
+        <v>8505</v>
       </c>
       <c r="D3" t="n">
-        <v>16031</v>
+        <v>13752</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2940</v>
+        <v>3382</v>
       </c>
       <c r="C4" t="n">
-        <v>4803</v>
+        <v>5512</v>
       </c>
       <c r="D4" t="n">
-        <v>10229</v>
+        <v>6830</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2289</v>
+        <v>2511</v>
       </c>
       <c r="C5" t="n">
-        <v>4163</v>
+        <v>4694</v>
       </c>
       <c r="D5" t="n">
-        <v>4690</v>
+        <v>2984</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1495</v>
+        <v>1724</v>
       </c>
       <c r="C6" t="n">
-        <v>3483</v>
+        <v>3629</v>
       </c>
       <c r="D6" t="n">
-        <v>1862</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>753</v>
+        <v>978</v>
       </c>
       <c r="C7" t="n">
-        <v>2598</v>
+        <v>2624</v>
       </c>
       <c r="D7" t="n">
-        <v>848</v>
+        <v>751</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>318</v>
+        <v>449</v>
       </c>
       <c r="C8" t="n">
-        <v>1714</v>
+        <v>1609</v>
       </c>
       <c r="D8" t="n">
-        <v>497</v>
+        <v>489</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>124</v>
+        <v>172</v>
       </c>
       <c r="C9" t="n">
-        <v>907</v>
+        <v>737</v>
       </c>
       <c r="D9" t="n">
-        <v>329</v>
+        <v>335</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="C10" t="n">
-        <v>422</v>
+        <v>328</v>
       </c>
       <c r="D10" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C11" t="n">
-        <v>224</v>
+        <v>202</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1573,7 +1573,7 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D14" t="n">
         <v>102</v>
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7725</v>
+        <v>8541</v>
       </c>
       <c r="C2" t="n">
-        <v>6683</v>
+        <v>7116</v>
       </c>
       <c r="D2" t="n">
-        <v>16578</v>
+        <v>25818</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5172</v>
+        <v>6222</v>
       </c>
       <c r="C3" t="n">
-        <v>8693</v>
+        <v>11742</v>
       </c>
       <c r="D3" t="n">
-        <v>17916</v>
+        <v>14706</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2115</v>
+        <v>2320</v>
       </c>
       <c r="C4" t="n">
-        <v>6670</v>
+        <v>7575</v>
       </c>
       <c r="D4" t="n">
-        <v>9919</v>
+        <v>6558</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1381</v>
+        <v>1592</v>
       </c>
       <c r="C5" t="n">
-        <v>3413</v>
+        <v>3556</v>
       </c>
       <c r="D5" t="n">
-        <v>3085</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>695</v>
+        <v>903</v>
       </c>
       <c r="C6" t="n">
-        <v>2546</v>
+        <v>2571</v>
       </c>
       <c r="D6" t="n">
-        <v>831</v>
+        <v>735</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>293</v>
+        <v>414</v>
       </c>
       <c r="C7" t="n">
-        <v>1679</v>
+        <v>1576</v>
       </c>
       <c r="D7" t="n">
-        <v>487</v>
+        <v>479</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>158</v>
       </c>
       <c r="C8" t="n">
-        <v>888</v>
+        <v>722</v>
       </c>
       <c r="D8" t="n">
-        <v>322</v>
+        <v>328</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="C9" t="n">
-        <v>413</v>
+        <v>321</v>
       </c>
       <c r="D9" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="D10" t="n">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13">
@@ -1870,7 +1870,7 @@
         <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D13" t="n">
         <v>99</v>
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D16" t="n">
         <v>50</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4633</v>
+        <v>5324</v>
       </c>
       <c r="C2" t="n">
-        <v>3129</v>
+        <v>3199</v>
       </c>
       <c r="D2" t="n">
-        <v>11675</v>
+        <v>19069</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5380</v>
+        <v>6247</v>
       </c>
       <c r="C3" t="n">
-        <v>7119</v>
+        <v>8709</v>
       </c>
       <c r="D3" t="n">
-        <v>16702</v>
+        <v>15370</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2849</v>
+        <v>3318</v>
       </c>
       <c r="C4" t="n">
-        <v>7655</v>
+        <v>9595</v>
       </c>
       <c r="D4" t="n">
-        <v>11036</v>
+        <v>7736</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1560</v>
+        <v>1778</v>
       </c>
       <c r="C5" t="n">
-        <v>4850</v>
+        <v>5350</v>
       </c>
       <c r="D5" t="n">
-        <v>3903</v>
+        <v>2695</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>837</v>
+        <v>1082</v>
       </c>
       <c r="C6" t="n">
-        <v>2975</v>
+        <v>3077</v>
       </c>
       <c r="D6" t="n">
-        <v>1061</v>
+        <v>885</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>276</v>
+        <v>388</v>
       </c>
       <c r="C7" t="n">
-        <v>2064</v>
+        <v>1971</v>
       </c>
       <c r="D7" t="n">
-        <v>533</v>
+        <v>520</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>96</v>
+        <v>131</v>
       </c>
       <c r="C8" t="n">
-        <v>1152</v>
+        <v>979</v>
       </c>
       <c r="D8" t="n">
-        <v>336</v>
+        <v>342</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>462</v>
+        <v>374</v>
       </c>
       <c r="D9" t="n">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5085</v>
+        <v>5959</v>
       </c>
       <c r="C2" t="n">
-        <v>3911</v>
+        <v>8201</v>
       </c>
       <c r="D2" t="n">
-        <v>17162</v>
+        <v>19800</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4252</v>
+        <v>4918</v>
       </c>
       <c r="C3" t="n">
-        <v>4650</v>
+        <v>5343</v>
       </c>
       <c r="D3" t="n">
-        <v>14989</v>
+        <v>14992</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3405</v>
+        <v>3959</v>
       </c>
       <c r="C4" t="n">
-        <v>7233</v>
+        <v>8953</v>
       </c>
       <c r="D4" t="n">
-        <v>11625</v>
+        <v>8672</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1869</v>
+        <v>2153</v>
       </c>
       <c r="C5" t="n">
-        <v>6068</v>
+        <v>7327</v>
       </c>
       <c r="D5" t="n">
-        <v>4879</v>
+        <v>3435</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1037</v>
+        <v>1261</v>
       </c>
       <c r="C6" t="n">
-        <v>3821</v>
+        <v>4072</v>
       </c>
       <c r="D6" t="n">
-        <v>1456</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>436</v>
+        <v>584</v>
       </c>
       <c r="C7" t="n">
-        <v>2455</v>
+        <v>2477</v>
       </c>
       <c r="D7" t="n">
-        <v>600</v>
+        <v>573</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>140</v>
+        <v>194</v>
       </c>
       <c r="C8" t="n">
-        <v>1538</v>
+        <v>1396</v>
       </c>
       <c r="D8" t="n">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>734</v>
+        <v>608</v>
       </c>
       <c r="D9" t="n">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>316</v>
+        <v>277</v>
       </c>
       <c r="D10" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2579,7 +2579,7 @@
         <v>59</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3013</v>
+        <v>3556</v>
       </c>
       <c r="C2" t="n">
-        <v>1819</v>
+        <v>3832</v>
       </c>
       <c r="D2" t="n">
-        <v>11864</v>
+        <v>13792</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4295</v>
+        <v>4986</v>
       </c>
       <c r="C3" t="n">
-        <v>4246</v>
+        <v>6089</v>
       </c>
       <c r="D3" t="n">
-        <v>14872</v>
+        <v>15156</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3753</v>
+        <v>4357</v>
       </c>
       <c r="C4" t="n">
-        <v>6978</v>
+        <v>8499</v>
       </c>
       <c r="D4" t="n">
-        <v>12310</v>
+        <v>9403</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1918</v>
+        <v>2243</v>
       </c>
       <c r="C5" t="n">
-        <v>7190</v>
+        <v>8702</v>
       </c>
       <c r="D5" t="n">
-        <v>5128</v>
+        <v>3638</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>824</v>
+        <v>1052</v>
       </c>
       <c r="C6" t="n">
-        <v>4676</v>
+        <v>4989</v>
       </c>
       <c r="D6" t="n">
-        <v>1416</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>179</v>
       </c>
       <c r="C7" t="n">
-        <v>2660</v>
+        <v>2580</v>
       </c>
       <c r="D7" t="n">
-        <v>594</v>
+        <v>576</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="C8" t="n">
-        <v>1201</v>
+        <v>1033</v>
       </c>
       <c r="D8" t="n">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>309</v>
+        <v>271</v>
       </c>
       <c r="D9" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2876,7 +2876,7 @@
         <v>57</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3268</v>
+        <v>4300</v>
       </c>
       <c r="C2" t="n">
-        <v>3979</v>
+        <v>9456</v>
       </c>
       <c r="D2" t="n">
-        <v>10125</v>
+        <v>11459</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3207</v>
+        <v>3757</v>
       </c>
       <c r="C3" t="n">
-        <v>2780</v>
+        <v>4486</v>
       </c>
       <c r="D3" t="n">
-        <v>13463</v>
+        <v>13952</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3510</v>
+        <v>4032</v>
       </c>
       <c r="C4" t="n">
-        <v>5588</v>
+        <v>7247</v>
       </c>
       <c r="D4" t="n">
-        <v>12353</v>
+        <v>10056</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2356</v>
+        <v>2745</v>
       </c>
       <c r="C5" t="n">
-        <v>7013</v>
+        <v>8512</v>
       </c>
       <c r="D5" t="n">
-        <v>6124</v>
+        <v>4447</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1122</v>
+        <v>1372</v>
       </c>
       <c r="C6" t="n">
-        <v>5740</v>
+        <v>6560</v>
       </c>
       <c r="D6" t="n">
-        <v>1896</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>298</v>
+        <v>391</v>
       </c>
       <c r="C7" t="n">
-        <v>3521</v>
+        <v>3597</v>
       </c>
       <c r="D7" t="n">
-        <v>698</v>
+        <v>648</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="C8" t="n">
-        <v>1753</v>
+        <v>1613</v>
       </c>
       <c r="D8" t="n">
-        <v>395</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>606</v>
+        <v>525</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2446</v>
+        <v>3177</v>
       </c>
       <c r="C2" t="n">
-        <v>2373</v>
+        <v>5766</v>
       </c>
       <c r="D2" t="n">
-        <v>7968</v>
+        <v>8403</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2826</v>
+        <v>3444</v>
       </c>
       <c r="C3" t="n">
-        <v>2985</v>
+        <v>5901</v>
       </c>
       <c r="D3" t="n">
-        <v>12330</v>
+        <v>12893</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3149</v>
+        <v>3605</v>
       </c>
       <c r="C4" t="n">
-        <v>4473</v>
+        <v>6122</v>
       </c>
       <c r="D4" t="n">
-        <v>12245</v>
+        <v>10370</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2581</v>
+        <v>2996</v>
       </c>
       <c r="C5" t="n">
-        <v>6549</v>
+        <v>8200</v>
       </c>
       <c r="D5" t="n">
-        <v>6772</v>
+        <v>5043</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1328</v>
+        <v>1626</v>
       </c>
       <c r="C6" t="n">
-        <v>6384</v>
+        <v>7436</v>
       </c>
       <c r="D6" t="n">
-        <v>2275</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>281</v>
+        <v>352</v>
       </c>
       <c r="C7" t="n">
-        <v>4326</v>
+        <v>4568</v>
       </c>
       <c r="D7" t="n">
-        <v>796</v>
+        <v>726</v>
       </c>
     </row>
     <row r="8">
@@ -3352,10 +3352,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>2242</v>
+        <v>2091</v>
       </c>
       <c r="D8" t="n">
         <v>412</v>
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>701</v>
+        <v>613</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3466</v>
+        <v>5048</v>
       </c>
       <c r="C2" t="n">
-        <v>6758</v>
+        <v>8627</v>
       </c>
       <c r="D2" t="n">
-        <v>15500</v>
+        <v>12619</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2260</v>
+        <v>2818</v>
       </c>
       <c r="C3" t="n">
-        <v>2449</v>
+        <v>5202</v>
       </c>
       <c r="D3" t="n">
-        <v>11017</v>
+        <v>11529</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2661</v>
+        <v>3114</v>
       </c>
       <c r="C4" t="n">
-        <v>3737</v>
+        <v>5901</v>
       </c>
       <c r="D4" t="n">
-        <v>11884</v>
+        <v>10418</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2533</v>
+        <v>2923</v>
       </c>
       <c r="C5" t="n">
-        <v>5555</v>
+        <v>7191</v>
       </c>
       <c r="D5" t="n">
-        <v>7236</v>
+        <v>5605</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1634</v>
+        <v>1939</v>
       </c>
       <c r="C6" t="n">
-        <v>6394</v>
+        <v>7666</v>
       </c>
       <c r="D6" t="n">
-        <v>2849</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>547</v>
+        <v>664</v>
       </c>
       <c r="C7" t="n">
-        <v>5110</v>
+        <v>5634</v>
       </c>
       <c r="D7" t="n">
-        <v>976</v>
+        <v>836</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>3018</v>
+        <v>2984</v>
       </c>
       <c r="D8" t="n">
-        <v>452</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>1221</v>
+        <v>1096</v>
       </c>
       <c r="D9" t="n">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>375</v>
+        <v>339</v>
       </c>
       <c r="D10" t="n">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12">
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D12" t="n">
         <v>95</v>
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>39</v>
+      </c>
+      <c r="D14" t="n">
         <v>38</v>
-      </c>
-      <c r="D14" t="n">
-        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4550</v>
+        <v>6973</v>
       </c>
       <c r="C2" t="n">
-        <v>9719</v>
+        <v>2850</v>
       </c>
       <c r="D2" t="n">
-        <v>11403</v>
+        <v>9935</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2455</v>
+        <v>3653</v>
       </c>
       <c r="C2" t="n">
-        <v>3785</v>
+        <v>4969</v>
       </c>
       <c r="D2" t="n">
-        <v>11408</v>
+        <v>9388</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3097</v>
+        <v>3812</v>
       </c>
       <c r="C3" t="n">
-        <v>3690</v>
+        <v>6426</v>
       </c>
       <c r="D3" t="n">
-        <v>12366</v>
+        <v>12474</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3675</v>
+        <v>4291</v>
       </c>
       <c r="C4" t="n">
-        <v>5522</v>
+        <v>8442</v>
       </c>
       <c r="D4" t="n">
-        <v>12277</v>
+        <v>10646</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1603</v>
+        <v>1845</v>
       </c>
       <c r="C5" t="n">
-        <v>8629</v>
+        <v>10710</v>
       </c>
       <c r="D5" t="n">
-        <v>6675</v>
+        <v>5075</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>505</v>
+        <v>613</v>
       </c>
       <c r="C6" t="n">
-        <v>6323</v>
+        <v>6948</v>
       </c>
       <c r="D6" t="n">
-        <v>2228</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="C7" t="n">
-        <v>2957</v>
+        <v>2924</v>
       </c>
       <c r="D7" t="n">
-        <v>567</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C8" t="n">
-        <v>1196</v>
+        <v>1074</v>
       </c>
       <c r="D8" t="n">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>367</v>
+        <v>332</v>
       </c>
       <c r="D9" t="n">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11">
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D11" t="n">
         <v>93</v>
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>38</v>
+      </c>
+      <c r="D13" t="n">
         <v>37</v>
-      </c>
-      <c r="D13" t="n">
-        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5725</v>
+        <v>7196</v>
       </c>
       <c r="C2" t="n">
-        <v>6370</v>
+        <v>7333</v>
       </c>
       <c r="D2" t="n">
-        <v>22597</v>
+        <v>8862</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1934</v>
+        <v>2962</v>
       </c>
       <c r="C3" t="n">
-        <v>4898</v>
+        <v>1436</v>
       </c>
       <c r="D3" t="n">
-        <v>2555</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4435</v>
+        <v>5481</v>
       </c>
       <c r="C2" t="n">
-        <v>3714</v>
+        <v>8374</v>
       </c>
       <c r="D2" t="n">
-        <v>30876</v>
+        <v>12562</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3143</v>
+        <v>4172</v>
       </c>
       <c r="C3" t="n">
-        <v>4942</v>
+        <v>4161</v>
       </c>
       <c r="D3" t="n">
-        <v>5734</v>
+        <v>3239</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>874</v>
+        <v>1320</v>
       </c>
       <c r="C4" t="n">
-        <v>2914</v>
+        <v>898</v>
       </c>
       <c r="D4" t="n">
-        <v>1696</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C6" t="n">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
@@ -4949,10 +4949,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5801</v>
+        <v>7206</v>
       </c>
       <c r="C2" t="n">
-        <v>6220</v>
+        <v>5237</v>
       </c>
       <c r="D2" t="n">
-        <v>27301</v>
+        <v>18358</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3104</v>
+        <v>4005</v>
       </c>
       <c r="C3" t="n">
-        <v>3715</v>
+        <v>5590</v>
       </c>
       <c r="D3" t="n">
-        <v>9343</v>
+        <v>4497</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1706</v>
+        <v>2326</v>
       </c>
       <c r="C4" t="n">
-        <v>3954</v>
+        <v>2718</v>
       </c>
       <c r="D4" t="n">
-        <v>2419</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>412</v>
+        <v>602</v>
       </c>
       <c r="C5" t="n">
-        <v>1690</v>
+        <v>592</v>
       </c>
       <c r="D5" t="n">
-        <v>1240</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5308,7 +5308,7 @@
         <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5361,7 +5361,7 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6933</v>
+        <v>7032</v>
       </c>
       <c r="C2" t="n">
-        <v>5844</v>
+        <v>6321</v>
       </c>
       <c r="D2" t="n">
-        <v>25686</v>
+        <v>15011</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3562</v>
+        <v>4517</v>
       </c>
       <c r="C3" t="n">
-        <v>4355</v>
+        <v>4695</v>
       </c>
       <c r="D3" t="n">
-        <v>11414</v>
+        <v>6287</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2015</v>
+        <v>2673</v>
       </c>
       <c r="C4" t="n">
-        <v>3743</v>
+        <v>4233</v>
       </c>
       <c r="D4" t="n">
-        <v>3608</v>
+        <v>2298</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>871</v>
+        <v>1223</v>
       </c>
       <c r="C5" t="n">
-        <v>2828</v>
+        <v>1702</v>
       </c>
       <c r="D5" t="n">
-        <v>1394</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>243</v>
+        <v>321</v>
       </c>
       <c r="C6" t="n">
-        <v>989</v>
+        <v>443</v>
       </c>
       <c r="D6" t="n">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C9" t="n">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5619,7 +5619,7 @@
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5686,7 +5686,7 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8317</v>
+        <v>6851</v>
       </c>
       <c r="C2" t="n">
-        <v>7325</v>
+        <v>4578</v>
       </c>
       <c r="D2" t="n">
-        <v>37899</v>
+        <v>23583</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3767</v>
+        <v>4195</v>
       </c>
       <c r="C3" t="n">
-        <v>4181</v>
+        <v>4536</v>
       </c>
       <c r="D3" t="n">
-        <v>12023</v>
+        <v>6746</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1728</v>
+        <v>2245</v>
       </c>
       <c r="C4" t="n">
-        <v>3305</v>
+        <v>3684</v>
       </c>
       <c r="D4" t="n">
-        <v>4295</v>
+        <v>2559</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>744</v>
+        <v>1016</v>
       </c>
       <c r="C5" t="n">
-        <v>2407</v>
+        <v>2214</v>
       </c>
       <c r="D5" t="n">
-        <v>1393</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>261</v>
+        <v>367</v>
       </c>
       <c r="C6" t="n">
-        <v>1271</v>
+        <v>734</v>
       </c>
       <c r="D6" t="n">
-        <v>782</v>
+        <v>763</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>424</v>
+        <v>255</v>
       </c>
       <c r="D7" t="n">
-        <v>514</v>
+        <v>520</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
         <v>222</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9">
@@ -5854,10 +5854,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D9" t="n">
         <v>270</v>
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
         <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13">
@@ -5916,7 +5916,7 @@
         <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14">
@@ -5930,7 +5930,7 @@
         <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -5972,7 +5972,7 @@
         <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -5983,7 +5983,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6025,10 +6025,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6392</v>
+        <v>7082</v>
       </c>
       <c r="C2" t="n">
-        <v>5248</v>
+        <v>10081</v>
       </c>
       <c r="D2" t="n">
-        <v>28818</v>
+        <v>20142</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5000</v>
+        <v>4603</v>
       </c>
       <c r="C3" t="n">
-        <v>5176</v>
+        <v>3911</v>
       </c>
       <c r="D3" t="n">
-        <v>15485</v>
+        <v>9202</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2405</v>
+        <v>2848</v>
       </c>
       <c r="C4" t="n">
-        <v>3766</v>
+        <v>4130</v>
       </c>
       <c r="D4" t="n">
-        <v>5681</v>
+        <v>3365</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1086</v>
+        <v>1464</v>
       </c>
       <c r="C5" t="n">
-        <v>2882</v>
+        <v>3021</v>
       </c>
       <c r="D5" t="n">
-        <v>1935</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>464</v>
+        <v>642</v>
       </c>
       <c r="C6" t="n">
-        <v>1898</v>
+        <v>1591</v>
       </c>
       <c r="D6" t="n">
-        <v>888</v>
+        <v>823</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>156</v>
+        <v>216</v>
       </c>
       <c r="C7" t="n">
-        <v>896</v>
+        <v>531</v>
       </c>
       <c r="D7" t="n">
-        <v>553</v>
+        <v>562</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>330</v>
+        <v>240</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D10" t="n">
-        <v>236</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13">
@@ -6224,7 +6224,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D13" t="n">
         <v>119</v>
@@ -6238,10 +6238,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
         <v>80</v>
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6294,10 +6294,10 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6311,7 +6311,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6339,7 +6339,7 @@
         <v>84</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4846</v>
+        <v>6836</v>
       </c>
       <c r="C2" t="n">
-        <v>7575</v>
+        <v>7960</v>
       </c>
       <c r="D2" t="n">
-        <v>24437</v>
+        <v>23336</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4720</v>
+        <v>4793</v>
       </c>
       <c r="C3" t="n">
-        <v>4522</v>
+        <v>6340</v>
       </c>
       <c r="D3" t="n">
-        <v>16503</v>
+        <v>10289</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3130</v>
+        <v>3222</v>
       </c>
       <c r="C4" t="n">
-        <v>4472</v>
+        <v>3917</v>
       </c>
       <c r="D4" t="n">
-        <v>7390</v>
+        <v>4351</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1514</v>
+        <v>1881</v>
       </c>
       <c r="C5" t="n">
-        <v>3269</v>
+        <v>3546</v>
       </c>
       <c r="D5" t="n">
-        <v>2540</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>691</v>
+        <v>962</v>
       </c>
       <c r="C6" t="n">
-        <v>2395</v>
+        <v>2354</v>
       </c>
       <c r="D6" t="n">
-        <v>1066</v>
+        <v>911</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>272</v>
+        <v>378</v>
       </c>
       <c r="C7" t="n">
-        <v>1416</v>
+        <v>1102</v>
       </c>
       <c r="D7" t="n">
-        <v>606</v>
+        <v>604</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="C8" t="n">
-        <v>612</v>
+        <v>391</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>415</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>225</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -6591,7 +6591,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -6650,7 +6650,7 @@
         <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_2_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_2_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6811</v>
+        <v>1042</v>
       </c>
       <c r="C2" t="n">
-        <v>7212</v>
+        <v>3220</v>
       </c>
       <c r="D2" t="n">
-        <v>20755</v>
+        <v>13489</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4720</v>
+        <v>1584</v>
       </c>
       <c r="C3" t="n">
-        <v>6244</v>
+        <v>7389</v>
       </c>
       <c r="D3" t="n">
-        <v>11547</v>
+        <v>12320</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3388</v>
+        <v>1045</v>
       </c>
       <c r="C4" t="n">
-        <v>5138</v>
+        <v>9756</v>
       </c>
       <c r="D4" t="n">
-        <v>5301</v>
+        <v>5580</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2225</v>
+        <v>562</v>
       </c>
       <c r="C5" t="n">
-        <v>3664</v>
+        <v>6908</v>
       </c>
       <c r="D5" t="n">
-        <v>2127</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1262</v>
+        <v>243</v>
       </c>
       <c r="C6" t="n">
-        <v>2900</v>
+        <v>3065</v>
       </c>
       <c r="D6" t="n">
-        <v>1042</v>
+        <v>724</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>579</v>
+        <v>96</v>
       </c>
       <c r="C7" t="n">
-        <v>1727</v>
+        <v>1047</v>
       </c>
       <c r="D7" t="n">
-        <v>643</v>
+        <v>496</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>214</v>
+        <v>71</v>
       </c>
       <c r="C8" t="n">
-        <v>732</v>
+        <v>378</v>
       </c>
       <c r="D8" t="n">
-        <v>442</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>299</v>
+        <v>270</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>264</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>137</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>139</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9040</v>
+        <v>1641</v>
       </c>
       <c r="C2" t="n">
-        <v>14831</v>
+        <v>5651</v>
       </c>
       <c r="D2" t="n">
-        <v>31694</v>
+        <v>16221</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4635</v>
+        <v>1139</v>
       </c>
       <c r="C3" t="n">
-        <v>5879</v>
+        <v>4608</v>
       </c>
       <c r="D3" t="n">
-        <v>12023</v>
+        <v>11748</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3432</v>
+        <v>1110</v>
       </c>
       <c r="C4" t="n">
-        <v>5523</v>
+        <v>8396</v>
       </c>
       <c r="D4" t="n">
-        <v>6108</v>
+        <v>6575</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2417</v>
+        <v>695</v>
       </c>
       <c r="C5" t="n">
-        <v>4295</v>
+        <v>8186</v>
       </c>
       <c r="D5" t="n">
-        <v>2580</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1533</v>
+        <v>343</v>
       </c>
       <c r="C6" t="n">
-        <v>3194</v>
+        <v>4907</v>
       </c>
       <c r="D6" t="n">
-        <v>1184</v>
+        <v>886</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>791</v>
+        <v>139</v>
       </c>
       <c r="C7" t="n">
-        <v>2266</v>
+        <v>1986</v>
       </c>
       <c r="D7" t="n">
-        <v>699</v>
+        <v>524</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>324</v>
+        <v>76</v>
       </c>
       <c r="C8" t="n">
-        <v>1170</v>
+        <v>670</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9">
@@ -1189,10 +1189,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>116</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>478</v>
+        <v>318</v>
       </c>
       <c r="D9" t="n">
         <v>325</v>
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>267</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>74</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9268</v>
+        <v>892</v>
       </c>
       <c r="C2" t="n">
-        <v>10590</v>
+        <v>2517</v>
       </c>
       <c r="D2" t="n">
-        <v>31613</v>
+        <v>11097</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5229</v>
+        <v>1225</v>
       </c>
       <c r="C3" t="n">
-        <v>8505</v>
+        <v>4822</v>
       </c>
       <c r="D3" t="n">
-        <v>13752</v>
+        <v>11984</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3382</v>
+        <v>1219</v>
       </c>
       <c r="C4" t="n">
-        <v>5512</v>
+        <v>7645</v>
       </c>
       <c r="D4" t="n">
-        <v>6830</v>
+        <v>7236</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2511</v>
+        <v>700</v>
       </c>
       <c r="C5" t="n">
-        <v>4694</v>
+        <v>9343</v>
       </c>
       <c r="D5" t="n">
-        <v>2984</v>
+        <v>2706</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1724</v>
+        <v>277</v>
       </c>
       <c r="C6" t="n">
-        <v>3629</v>
+        <v>5984</v>
       </c>
       <c r="D6" t="n">
-        <v>1369</v>
+        <v>904</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>978</v>
+        <v>70</v>
       </c>
       <c r="C7" t="n">
-        <v>2624</v>
+        <v>1815</v>
       </c>
       <c r="D7" t="n">
-        <v>751</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>449</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>1609</v>
+        <v>534</v>
       </c>
       <c r="D8" t="n">
-        <v>489</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>172</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>737</v>
+        <v>230</v>
       </c>
       <c r="D9" t="n">
-        <v>335</v>
+        <v>360</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>64</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>328</v>
+        <v>183</v>
       </c>
       <c r="D10" t="n">
-        <v>256</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>202</v>
+        <v>127</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>120</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8541</v>
+        <v>649</v>
       </c>
       <c r="C2" t="n">
-        <v>7116</v>
+        <v>4243</v>
       </c>
       <c r="D2" t="n">
-        <v>25818</v>
+        <v>9956</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6222</v>
+        <v>919</v>
       </c>
       <c r="C3" t="n">
-        <v>11742</v>
+        <v>3289</v>
       </c>
       <c r="D3" t="n">
-        <v>14706</v>
+        <v>11031</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2320</v>
+        <v>1082</v>
       </c>
       <c r="C4" t="n">
-        <v>7575</v>
+        <v>6076</v>
       </c>
       <c r="D4" t="n">
-        <v>6558</v>
+        <v>7905</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1592</v>
+        <v>821</v>
       </c>
       <c r="C5" t="n">
-        <v>3556</v>
+        <v>8423</v>
       </c>
       <c r="D5" t="n">
-        <v>2172</v>
+        <v>3319</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>903</v>
+        <v>401</v>
       </c>
       <c r="C6" t="n">
-        <v>2571</v>
+        <v>7558</v>
       </c>
       <c r="D6" t="n">
-        <v>735</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>414</v>
+        <v>124</v>
       </c>
       <c r="C7" t="n">
-        <v>1576</v>
+        <v>3606</v>
       </c>
       <c r="D7" t="n">
-        <v>479</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>158</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>722</v>
+        <v>1033</v>
       </c>
       <c r="D8" t="n">
-        <v>328</v>
+        <v>442</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>321</v>
+        <v>340</v>
       </c>
       <c r="D9" t="n">
-        <v>250</v>
+        <v>366</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="D10" t="n">
-        <v>202</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>125</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>65</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5324</v>
+        <v>334</v>
       </c>
       <c r="C2" t="n">
-        <v>3199</v>
+        <v>3261</v>
       </c>
       <c r="D2" t="n">
-        <v>19069</v>
+        <v>8376</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6247</v>
+        <v>721</v>
       </c>
       <c r="C3" t="n">
-        <v>8709</v>
+        <v>3334</v>
       </c>
       <c r="D3" t="n">
-        <v>15370</v>
+        <v>10275</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3318</v>
+        <v>949</v>
       </c>
       <c r="C4" t="n">
-        <v>9595</v>
+        <v>4893</v>
       </c>
       <c r="D4" t="n">
-        <v>7736</v>
+        <v>8190</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1778</v>
+        <v>875</v>
       </c>
       <c r="C5" t="n">
-        <v>5350</v>
+        <v>7647</v>
       </c>
       <c r="D5" t="n">
-        <v>2695</v>
+        <v>3854</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1082</v>
+        <v>480</v>
       </c>
       <c r="C6" t="n">
-        <v>3077</v>
+        <v>8163</v>
       </c>
       <c r="D6" t="n">
-        <v>885</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>388</v>
+        <v>131</v>
       </c>
       <c r="C7" t="n">
-        <v>1971</v>
+        <v>4971</v>
       </c>
       <c r="D7" t="n">
-        <v>520</v>
+        <v>648</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>131</v>
+        <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>979</v>
+        <v>1584</v>
       </c>
       <c r="D8" t="n">
-        <v>342</v>
+        <v>468</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>374</v>
+        <v>437</v>
       </c>
       <c r="D9" t="n">
-        <v>259</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>169</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>95</v>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5959</v>
+        <v>1015</v>
       </c>
       <c r="C2" t="n">
-        <v>8201</v>
+        <v>17971</v>
       </c>
       <c r="D2" t="n">
-        <v>19800</v>
+        <v>9259</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4918</v>
+        <v>481</v>
       </c>
       <c r="C3" t="n">
-        <v>5343</v>
+        <v>2916</v>
       </c>
       <c r="D3" t="n">
-        <v>14992</v>
+        <v>9357</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3959</v>
+        <v>757</v>
       </c>
       <c r="C4" t="n">
-        <v>8953</v>
+        <v>4119</v>
       </c>
       <c r="D4" t="n">
-        <v>8672</v>
+        <v>8261</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2153</v>
+        <v>824</v>
       </c>
       <c r="C5" t="n">
-        <v>7327</v>
+        <v>6298</v>
       </c>
       <c r="D5" t="n">
-        <v>3435</v>
+        <v>4361</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1261</v>
+        <v>580</v>
       </c>
       <c r="C6" t="n">
-        <v>4072</v>
+        <v>7876</v>
       </c>
       <c r="D6" t="n">
-        <v>1151</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>584</v>
+        <v>225</v>
       </c>
       <c r="C7" t="n">
-        <v>2477</v>
+        <v>6300</v>
       </c>
       <c r="D7" t="n">
-        <v>573</v>
+        <v>734</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>194</v>
+        <v>67</v>
       </c>
       <c r="C8" t="n">
-        <v>1396</v>
+        <v>2844</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>608</v>
+        <v>845</v>
       </c>
       <c r="D9" t="n">
-        <v>266</v>
+        <v>370</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>277</v>
+        <v>294</v>
       </c>
       <c r="D10" t="n">
-        <v>215</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D12" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2495,7 +2495,7 @@
         <v>76</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>94</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3556</v>
+        <v>698</v>
       </c>
       <c r="C2" t="n">
-        <v>3832</v>
+        <v>9776</v>
       </c>
       <c r="D2" t="n">
-        <v>13792</v>
+        <v>6741</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4986</v>
+        <v>749</v>
       </c>
       <c r="C3" t="n">
-        <v>6089</v>
+        <v>7008</v>
       </c>
       <c r="D3" t="n">
-        <v>15156</v>
+        <v>10125</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4357</v>
+        <v>1142</v>
       </c>
       <c r="C4" t="n">
-        <v>8499</v>
+        <v>6159</v>
       </c>
       <c r="D4" t="n">
-        <v>9403</v>
+        <v>8459</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2243</v>
+        <v>573</v>
       </c>
       <c r="C5" t="n">
-        <v>8702</v>
+        <v>10175</v>
       </c>
       <c r="D5" t="n">
-        <v>3638</v>
+        <v>3994</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1052</v>
+        <v>207</v>
       </c>
       <c r="C6" t="n">
-        <v>4989</v>
+        <v>7949</v>
       </c>
       <c r="D6" t="n">
-        <v>1144</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>179</v>
+        <v>61</v>
       </c>
       <c r="C7" t="n">
-        <v>2580</v>
+        <v>2787</v>
       </c>
       <c r="D7" t="n">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="C8" t="n">
-        <v>1033</v>
+        <v>828</v>
       </c>
       <c r="D8" t="n">
-        <v>380</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>271</v>
+        <v>288</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>238</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -2792,7 +2792,7 @@
         <v>74</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>91</v>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4300</v>
+        <v>386</v>
       </c>
       <c r="C2" t="n">
-        <v>9456</v>
+        <v>4136</v>
       </c>
       <c r="D2" t="n">
-        <v>11459</v>
+        <v>5215</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3757</v>
+        <v>612</v>
       </c>
       <c r="C3" t="n">
-        <v>4486</v>
+        <v>7341</v>
       </c>
       <c r="D3" t="n">
-        <v>13952</v>
+        <v>8953</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4032</v>
+        <v>800</v>
       </c>
       <c r="C4" t="n">
-        <v>7247</v>
+        <v>6235</v>
       </c>
       <c r="D4" t="n">
-        <v>10056</v>
+        <v>8122</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2745</v>
+        <v>562</v>
       </c>
       <c r="C5" t="n">
-        <v>8512</v>
+        <v>7338</v>
       </c>
       <c r="D5" t="n">
-        <v>4447</v>
+        <v>4100</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1372</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>6560</v>
+        <v>7368</v>
       </c>
       <c r="D6" t="n">
-        <v>1464</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>391</v>
+        <v>49</v>
       </c>
       <c r="C7" t="n">
-        <v>3597</v>
+        <v>3522</v>
       </c>
       <c r="D7" t="n">
-        <v>648</v>
+        <v>551</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>82</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>1613</v>
+        <v>984</v>
       </c>
       <c r="D8" t="n">
-        <v>400</v>
+        <v>314</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>525</v>
+        <v>280</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>214</v>
+        <v>120</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>136</v>
+        <v>73</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3177</v>
+        <v>260</v>
       </c>
       <c r="C2" t="n">
-        <v>5766</v>
+        <v>7123</v>
       </c>
       <c r="D2" t="n">
-        <v>8403</v>
+        <v>6659</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3444</v>
+        <v>426</v>
       </c>
       <c r="C3" t="n">
-        <v>5901</v>
+        <v>4986</v>
       </c>
       <c r="D3" t="n">
-        <v>12893</v>
+        <v>7754</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3605</v>
+        <v>621</v>
       </c>
       <c r="C4" t="n">
-        <v>6122</v>
+        <v>6699</v>
       </c>
       <c r="D4" t="n">
-        <v>10370</v>
+        <v>8026</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2996</v>
+        <v>606</v>
       </c>
       <c r="C5" t="n">
-        <v>8200</v>
+        <v>6613</v>
       </c>
       <c r="D5" t="n">
-        <v>5043</v>
+        <v>4670</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1626</v>
+        <v>327</v>
       </c>
       <c r="C6" t="n">
-        <v>7436</v>
+        <v>7345</v>
       </c>
       <c r="D6" t="n">
-        <v>1732</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>352</v>
+        <v>99</v>
       </c>
       <c r="C7" t="n">
-        <v>4568</v>
+        <v>5401</v>
       </c>
       <c r="D7" t="n">
-        <v>726</v>
+        <v>699</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>2091</v>
+        <v>2127</v>
       </c>
       <c r="D8" t="n">
-        <v>412</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>613</v>
+        <v>588</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>202</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>183</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>136</v>
+        <v>91</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5048</v>
+        <v>455</v>
       </c>
       <c r="C2" t="n">
-        <v>8627</v>
+        <v>19530</v>
       </c>
       <c r="D2" t="n">
-        <v>12619</v>
+        <v>7942</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2818</v>
+        <v>299</v>
       </c>
       <c r="C3" t="n">
-        <v>5202</v>
+        <v>5251</v>
       </c>
       <c r="D3" t="n">
-        <v>11529</v>
+        <v>7084</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3114</v>
+        <v>464</v>
       </c>
       <c r="C4" t="n">
-        <v>5901</v>
+        <v>5720</v>
       </c>
       <c r="D4" t="n">
-        <v>10418</v>
+        <v>7660</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2923</v>
+        <v>558</v>
       </c>
       <c r="C5" t="n">
-        <v>7191</v>
+        <v>6452</v>
       </c>
       <c r="D5" t="n">
-        <v>5605</v>
+        <v>5075</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1939</v>
+        <v>408</v>
       </c>
       <c r="C6" t="n">
-        <v>7666</v>
+        <v>6934</v>
       </c>
       <c r="D6" t="n">
-        <v>2123</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>664</v>
+        <v>171</v>
       </c>
       <c r="C7" t="n">
-        <v>5634</v>
+        <v>6275</v>
       </c>
       <c r="D7" t="n">
-        <v>836</v>
+        <v>866</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>46</v>
       </c>
       <c r="C8" t="n">
-        <v>2984</v>
+        <v>3537</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>393</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>1096</v>
+        <v>1221</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>219</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="D11" t="n">
-        <v>141</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6973</v>
+        <v>3812</v>
       </c>
       <c r="C2" t="n">
-        <v>2850</v>
+        <v>21234</v>
       </c>
       <c r="D2" t="n">
-        <v>9935</v>
+        <v>11622</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3653</v>
+        <v>586</v>
       </c>
       <c r="C2" t="n">
-        <v>4969</v>
+        <v>18852</v>
       </c>
       <c r="D2" t="n">
-        <v>9388</v>
+        <v>8694</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3812</v>
+        <v>296</v>
       </c>
       <c r="C3" t="n">
-        <v>6426</v>
+        <v>9909</v>
       </c>
       <c r="D3" t="n">
-        <v>12474</v>
+        <v>6729</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4291</v>
+        <v>345</v>
       </c>
       <c r="C4" t="n">
-        <v>8442</v>
+        <v>5393</v>
       </c>
       <c r="D4" t="n">
-        <v>10646</v>
+        <v>7338</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1845</v>
+        <v>481</v>
       </c>
       <c r="C5" t="n">
-        <v>10710</v>
+        <v>5946</v>
       </c>
       <c r="D5" t="n">
-        <v>5075</v>
+        <v>5292</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>613</v>
+        <v>429</v>
       </c>
       <c r="C6" t="n">
-        <v>6948</v>
+        <v>6672</v>
       </c>
       <c r="D6" t="n">
-        <v>1753</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>119</v>
+        <v>235</v>
       </c>
       <c r="C7" t="n">
-        <v>2924</v>
+        <v>6475</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="C8" t="n">
-        <v>1074</v>
+        <v>4608</v>
       </c>
       <c r="D8" t="n">
-        <v>294</v>
+        <v>445</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>332</v>
+        <v>2082</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>238</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>156</v>
+        <v>647</v>
       </c>
       <c r="D10" t="n">
-        <v>138</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>93</v>
+        <v>199</v>
       </c>
       <c r="D11" t="n">
-        <v>93</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>60</v>
+      </c>
+      <c r="D13" t="n">
         <v>38</v>
-      </c>
-      <c r="D13" t="n">
-        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7196</v>
+        <v>4492</v>
       </c>
       <c r="C2" t="n">
-        <v>7333</v>
+        <v>12840</v>
       </c>
       <c r="D2" t="n">
-        <v>8862</v>
+        <v>17834</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2962</v>
+        <v>1231</v>
       </c>
       <c r="C3" t="n">
-        <v>1436</v>
+        <v>8385</v>
       </c>
       <c r="D3" t="n">
-        <v>2308</v>
+        <v>2201</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>149</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>338</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>141</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>356</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5481</v>
+        <v>2221</v>
       </c>
       <c r="C2" t="n">
-        <v>8374</v>
+        <v>6525</v>
       </c>
       <c r="D2" t="n">
-        <v>12562</v>
+        <v>18363</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4172</v>
+        <v>2433</v>
       </c>
       <c r="C3" t="n">
-        <v>4161</v>
+        <v>9471</v>
       </c>
       <c r="D3" t="n">
-        <v>3239</v>
+        <v>4786</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1320</v>
+        <v>585</v>
       </c>
       <c r="C4" t="n">
-        <v>898</v>
+        <v>5200</v>
       </c>
       <c r="D4" t="n">
-        <v>1646</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>136</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>341</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>321</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>315</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7206</v>
+        <v>1519</v>
       </c>
       <c r="C2" t="n">
-        <v>5237</v>
+        <v>8830</v>
       </c>
       <c r="D2" t="n">
-        <v>18358</v>
+        <v>21023</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4005</v>
+        <v>1921</v>
       </c>
       <c r="C3" t="n">
-        <v>5590</v>
+        <v>6730</v>
       </c>
       <c r="D3" t="n">
-        <v>4497</v>
+        <v>6714</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2326</v>
+        <v>1311</v>
       </c>
       <c r="C4" t="n">
-        <v>2718</v>
+        <v>7592</v>
       </c>
       <c r="D4" t="n">
-        <v>1901</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>602</v>
+        <v>292</v>
       </c>
       <c r="C5" t="n">
-        <v>592</v>
+        <v>3031</v>
       </c>
       <c r="D5" t="n">
-        <v>1222</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>146</v>
+        <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>264</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>784</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>331</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>89</v>
       </c>
       <c r="C8" t="n">
-        <v>355</v>
+        <v>283</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>215</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>327</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>252</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7032</v>
+        <v>1449</v>
       </c>
       <c r="C2" t="n">
-        <v>6321</v>
+        <v>7026</v>
       </c>
       <c r="D2" t="n">
-        <v>15011</v>
+        <v>22845</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4517</v>
+        <v>1434</v>
       </c>
       <c r="C3" t="n">
-        <v>4695</v>
+        <v>6810</v>
       </c>
       <c r="D3" t="n">
-        <v>6287</v>
+        <v>8520</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2673</v>
+        <v>1388</v>
       </c>
       <c r="C4" t="n">
-        <v>4233</v>
+        <v>6954</v>
       </c>
       <c r="D4" t="n">
-        <v>2298</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1223</v>
+        <v>662</v>
       </c>
       <c r="C5" t="n">
-        <v>1702</v>
+        <v>5419</v>
       </c>
       <c r="D5" t="n">
-        <v>1308</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>321</v>
+        <v>180</v>
       </c>
       <c r="C6" t="n">
-        <v>443</v>
+        <v>1695</v>
       </c>
       <c r="D6" t="n">
-        <v>951</v>
+        <v>822</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>296</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>381</v>
+        <v>306</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="C9" t="n">
-        <v>308</v>
+        <v>246</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>333</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>218</v>
+        <v>195</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6851</v>
+        <v>1677</v>
       </c>
       <c r="C2" t="n">
-        <v>4578</v>
+        <v>7846</v>
       </c>
       <c r="D2" t="n">
-        <v>23583</v>
+        <v>22769</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4195</v>
+        <v>1193</v>
       </c>
       <c r="C3" t="n">
-        <v>4536</v>
+        <v>6042</v>
       </c>
       <c r="D3" t="n">
-        <v>6746</v>
+        <v>9996</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2245</v>
+        <v>1223</v>
       </c>
       <c r="C4" t="n">
-        <v>3684</v>
+        <v>6734</v>
       </c>
       <c r="D4" t="n">
-        <v>2559</v>
+        <v>3811</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1016</v>
+        <v>863</v>
       </c>
       <c r="C5" t="n">
-        <v>2214</v>
+        <v>6072</v>
       </c>
       <c r="D5" t="n">
-        <v>1174</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>367</v>
+        <v>356</v>
       </c>
       <c r="C6" t="n">
-        <v>734</v>
+        <v>3448</v>
       </c>
       <c r="D6" t="n">
-        <v>763</v>
+        <v>884</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="C7" t="n">
-        <v>255</v>
+        <v>967</v>
       </c>
       <c r="D7" t="n">
-        <v>520</v>
+        <v>609</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>301</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="C9" t="n">
-        <v>200</v>
+        <v>272</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>340</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>171</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>143</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7082</v>
+        <v>2238</v>
       </c>
       <c r="C2" t="n">
-        <v>10081</v>
+        <v>10059</v>
       </c>
       <c r="D2" t="n">
-        <v>20142</v>
+        <v>23786</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4603</v>
+        <v>1153</v>
       </c>
       <c r="C3" t="n">
-        <v>3911</v>
+        <v>6038</v>
       </c>
       <c r="D3" t="n">
-        <v>9202</v>
+        <v>11061</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2848</v>
+        <v>1052</v>
       </c>
       <c r="C4" t="n">
-        <v>4130</v>
+        <v>6261</v>
       </c>
       <c r="D4" t="n">
-        <v>3365</v>
+        <v>4704</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1464</v>
+        <v>903</v>
       </c>
       <c r="C5" t="n">
-        <v>3021</v>
+        <v>6192</v>
       </c>
       <c r="D5" t="n">
-        <v>1417</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>642</v>
+        <v>518</v>
       </c>
       <c r="C6" t="n">
-        <v>1591</v>
+        <v>4598</v>
       </c>
       <c r="D6" t="n">
-        <v>823</v>
+        <v>970</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>216</v>
+        <v>196</v>
       </c>
       <c r="C7" t="n">
-        <v>531</v>
+        <v>2051</v>
       </c>
       <c r="D7" t="n">
-        <v>562</v>
+        <v>637</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="C8" t="n">
-        <v>240</v>
+        <v>588</v>
       </c>
       <c r="D8" t="n">
-        <v>389</v>
+        <v>467</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>283</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>348</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>175</v>
+        <v>232</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>186</v>
       </c>
       <c r="D11" t="n">
-        <v>196</v>
+        <v>263</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>153</v>
       </c>
       <c r="D12" t="n">
-        <v>154</v>
+        <v>204</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>125</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6836</v>
+        <v>1996</v>
       </c>
       <c r="C2" t="n">
-        <v>7960</v>
+        <v>6437</v>
       </c>
       <c r="D2" t="n">
-        <v>23336</v>
+        <v>18966</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4793</v>
+        <v>1672</v>
       </c>
       <c r="C3" t="n">
-        <v>6340</v>
+        <v>9689</v>
       </c>
       <c r="D3" t="n">
-        <v>10289</v>
+        <v>12035</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3222</v>
+        <v>834</v>
       </c>
       <c r="C4" t="n">
-        <v>3917</v>
+        <v>9670</v>
       </c>
       <c r="D4" t="n">
-        <v>4351</v>
+        <v>4380</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1881</v>
+        <v>478</v>
       </c>
       <c r="C5" t="n">
-        <v>3546</v>
+        <v>4506</v>
       </c>
       <c r="D5" t="n">
-        <v>1747</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>962</v>
+        <v>181</v>
       </c>
       <c r="C6" t="n">
-        <v>2354</v>
+        <v>2009</v>
       </c>
       <c r="D6" t="n">
-        <v>911</v>
+        <v>624</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>378</v>
+        <v>89</v>
       </c>
       <c r="C7" t="n">
-        <v>1102</v>
+        <v>576</v>
       </c>
       <c r="D7" t="n">
-        <v>604</v>
+        <v>457</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>126</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>391</v>
+        <v>277</v>
       </c>
       <c r="D8" t="n">
-        <v>415</v>
+        <v>341</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>142</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
